--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_14.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_14.xlsx
@@ -1128,14 +1128,14 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -1502,9 +1502,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1522,9 +1522,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1652,24 +1652,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
